--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD0AA6E-FE9E-4B08-83ED-BA23947286BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196B5BB5-7B88-45D6-A964-55CDE961D6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
+    <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -399,12 +399,48 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -414,12 +450,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -429,24 +459,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -454,27 +475,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -753,434 +753,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AC3B-8D90-4B0D-96EA-52FB68143200}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="5"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="14">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="14">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14">
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
         <f>ROUNDUP(I4*0.5,0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="2">
         <f>ROUND(I4*0.25,0)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="2">
         <f>ROUND(I4*0.15,0)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="2">
         <f>I4-E4-F4-G4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="2">
         <f>ROUND(C4*D4/100,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="14">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="14">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
         <f t="shared" ref="E5:E8" si="0">ROUNDUP(I5*0.5,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="2">
         <f t="shared" ref="F5:F8" si="1">ROUND(I5*0.25,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="2">
         <f t="shared" ref="G5:G8" si="2">ROUND(I5*0.15,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="2">
         <f t="shared" ref="H5:H8" si="3">I5-E5-F5-G5</f>
         <v>0</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="2">
         <f t="shared" ref="I5:I8" si="4">ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="14">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="14">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="14">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="14">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14">
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="14">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="14">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="14">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="14">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14">
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <f t="shared" ref="E9:E11" si="5">ROUNDUP(I9*0.5,0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="2">
         <f t="shared" ref="F9:F11" si="6">ROUND(I9*0.25,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="2">
         <f t="shared" ref="G9:G11" si="7">ROUND(I9*0.15,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="2">
         <f t="shared" ref="H9:H11" si="8">I9-E9-F9-G9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="2">
         <f t="shared" ref="I9:I11" si="9">ROUND(C9*D9/100,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="14">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14">
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="2">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="2">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="14">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="14">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14">
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="2">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="2">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="14">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="14">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
         <f t="shared" ref="E12:E14" si="10">ROUNDUP(I12*0.5,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="2">
         <f t="shared" ref="F12:F14" si="11">ROUND(I12*0.25,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="2">
         <f t="shared" ref="G12:G14" si="12">ROUND(I12*0.15,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="2">
         <f t="shared" ref="H12:H14" si="13">I12-E12-F12-G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="2">
         <f t="shared" ref="I12:I14" si="14">ROUND(C12*D12/100,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="14">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="14">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="2">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="2">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="2">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="2">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="14">
+      <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="14">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14">
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="2">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="2">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="2">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="2">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1200,361 +1200,361 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C04A3E4-2F16-400C-90BF-200CB05E84C8}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="19"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="17" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="17" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="16" t="s">
+      <c r="I2" s="26"/>
+      <c r="J2" s="21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="16" t="s">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="16" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22" t="s">
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="23">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="24">
-        <v>0</v>
-      </c>
-      <c r="D5" s="25">
-        <v>0</v>
-      </c>
-      <c r="E5" s="24">
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
         <f>ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="25">
-        <v>0</v>
-      </c>
-      <c r="G5" s="24">
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
         <f>ROUND(E5*F5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="25">
-        <v>0</v>
-      </c>
-      <c r="I5" s="24">
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
         <f>ROUND(H5*C5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="6">
         <f>E5+I5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="24">
-        <v>0</v>
-      </c>
-      <c r="D6" s="25">
-        <v>0</v>
-      </c>
-      <c r="E6" s="24">
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
         <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="7">
         <v>1</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="6">
         <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="6">
         <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="6">
         <f t="shared" ref="J6:J11" si="3">E6+I6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="24">
-        <v>0</v>
-      </c>
-      <c r="D7" s="25">
-        <v>0</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="7">
         <v>2</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="24">
-        <v>0</v>
-      </c>
-      <c r="D8" s="25">
-        <v>0</v>
-      </c>
-      <c r="E8" s="24">
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="7">
         <v>3</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="7">
         <v>3</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="24">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="7">
         <v>4</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="7">
         <v>4</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="24">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="24">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25">
-        <v>0</v>
-      </c>
-      <c r="E10" s="24">
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="7">
         <v>5</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="7">
         <v>5</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="24">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25">
-        <v>0</v>
-      </c>
-      <c r="E11" s="24">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="7">
         <v>6</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="7">
         <v>6</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24">
-      <c r="A12" s="23">
+      <c r="A12" s="5">
         <v>2</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="6">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="7">
         <v>8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="6">
         <f>ROUND(C12*D12/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="23" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196B5BB5-7B88-45D6-A964-55CDE961D6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D6E142-7F0C-42A9-85A5-F1DDBE98538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="8" r:id="rId2"/>
+    <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D6E142-7F0C-42A9-85A5-F1DDBE98538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957FCAC1-1DFD-4F0B-B02E-1954116D9074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
+    <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -154,13 +155,25 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Phân bổ chuyển thương</t>
+  </si>
+  <si>
+    <t>Cáng bộ</t>
+  </si>
+  <si>
+    <t>Tự đi</t>
+  </si>
+  <si>
+    <t>Tổng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,8 +214,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,6 +254,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -397,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -477,6 +504,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1573,4 +1619,311 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC69830-15C2-40EF-A85C-0B734C645A25}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="28"/>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="26"/>
+      <c r="J2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="26"/>
+      <c r="H3" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="22"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <f>ROUND(C5*D5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <f>ROUND(E5*F5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <f>ROUND(H5*C5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <f>E5+I5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="33">
+        <f>ROUNDUP(J5/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="33">
+        <f>J5-K5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="33">
+        <f>J5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+    </row>
+    <row r="7" spans="1:13" ht="24">
+      <c r="A7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+    </row>
+    <row r="12" spans="1:13" ht="24">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <f>ROUND(C12*D12/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:C4"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957FCAC1-1DFD-4F0B-B02E-1954116D9074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A65D87-F26B-4B2C-BBC7-99C41E8488E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -450,6 +450,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -486,43 +523,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -799,48 +799,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AC3B-8D90-4B0D-96EA-52FB68143200}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="17"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="11"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1246,82 +1246,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C04A3E4-2F16-400C-90BF-200CB05E84C8}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="24" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="21" t="s">
+      <c r="I2" s="16"/>
+      <c r="J2" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="21" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="22"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
@@ -1624,105 +1624,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC69830-15C2-40EF-A85C-0B734C645A25}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="27" t="s">
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="29"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="24" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="21" t="s">
+      <c r="I2" s="16"/>
+      <c r="J2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="21" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="22"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5">
@@ -1759,15 +1759,15 @@
         <f>E5+I5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="9">
         <f>ROUNDUP(J5/2,0)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="9">
         <f>J5-K5</f>
         <v>0</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="9">
         <f>J5</f>
         <v>0</v>
       </c>
@@ -1779,17 +1779,40 @@
       <c r="B6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6">
+        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
+        <v>0</v>
+      </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6">
+        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
+        <v>0</v>
+      </c>
       <c r="H6" s="8"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
+      <c r="I6" s="6">
+        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" ref="K6:K11" si="4">ROUNDUP(J6/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <f t="shared" ref="L6:L11" si="5">J6-K6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" ref="M6:M11" si="6">J6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="24">
       <c r="A7" s="5" t="s">
@@ -1798,85 +1821,208 @@
       <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H7" s="8"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="I7" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H8" s="8"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="I8" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="24">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H9" s="8"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="I9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24">
       <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H10" s="8"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
+      <c r="I10" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H11" s="8"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
+      <c r="I11" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="24">
       <c r="A12" s="5">
@@ -1901,18 +2047,12 @@
       <c r="H12" s="8"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:C4"/>
@@ -1923,6 +2063,12 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A65D87-F26B-4B2C-BBC7-99C41E8488E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F4D111-C1D1-4C62-9072-5C5E8256620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
     <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId3"/>
+    <sheet name="Trang_tính1" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="63">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -167,13 +168,70 @@
   </si>
   <si>
     <t>Tổng</t>
+  </si>
+  <si>
+    <t>Loại TBKT</t>
+  </si>
+  <si>
+    <t>Dự kiến tỉ lệ hư hỏng 1 ngày đêm (%)</t>
+  </si>
+  <si>
+    <t>Khả năng sửa chữa trong 1 ngày đêm</t>
+  </si>
+  <si>
+    <t>Còn lại chưa sửa chữa được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhẹ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nặng </t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>GĐ CB CĐ</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>GĐ TH CĐ</t>
+  </si>
+  <si>
+    <t>SMPK 12,7mm</t>
+  </si>
+  <si>
+    <t>Cối 100mm</t>
+  </si>
+  <si>
+    <t>Cối 82mm</t>
+  </si>
+  <si>
+    <t>Cối 60mm</t>
+  </si>
+  <si>
+    <t>Súng SPG-9</t>
+  </si>
+  <si>
+    <t>Súng B41</t>
+  </si>
+  <si>
+    <t>Súng đại liên</t>
+  </si>
+  <si>
+    <t>Súng trung liên</t>
+  </si>
+  <si>
+    <t>Súng tiểu liên</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,8 +280,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,8 +344,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -420,11 +510,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -451,6 +641,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -460,33 +677,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -522,6 +712,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1249,79 +1481,79 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="16"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="15" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="15" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="13" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
@@ -1627,102 +1859,102 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="19" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="15" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="15" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="13" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5">
@@ -2072,4 +2304,524 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="5" max="9" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
+      <c r="A1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
+    </row>
+    <row r="2" spans="1:17" ht="32.4" customHeight="1" thickBot="1">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="27" thickBot="1">
+      <c r="A3" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+    </row>
+    <row r="4" spans="1:17" ht="27" thickBot="1">
+      <c r="A4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+    </row>
+    <row r="5" spans="1:17" ht="27" thickBot="1">
+      <c r="A5" s="44">
+        <v>1</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="40">
+        <v>9</v>
+      </c>
+      <c r="D5" s="46">
+        <v>8</v>
+      </c>
+      <c r="E5" s="46">
+        <v>1</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="47">
+        <v>1</v>
+      </c>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46">
+        <v>1</v>
+      </c>
+      <c r="N5" s="46">
+        <v>0</v>
+      </c>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="27" thickBot="1">
+      <c r="A6" s="44">
+        <v>2</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="40">
+        <v>4</v>
+      </c>
+      <c r="D6" s="46">
+        <v>9</v>
+      </c>
+      <c r="E6" s="46">
+        <v>1</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="47">
+        <v>1</v>
+      </c>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46">
+        <v>1</v>
+      </c>
+      <c r="N6" s="46">
+        <v>0</v>
+      </c>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="27" thickBot="1">
+      <c r="A7" s="44">
+        <v>3</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="40">
+        <v>4</v>
+      </c>
+      <c r="D7" s="46">
+        <v>9</v>
+      </c>
+      <c r="E7" s="46">
+        <v>1</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47">
+        <v>1</v>
+      </c>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46">
+        <v>1</v>
+      </c>
+      <c r="N7" s="46">
+        <v>0</v>
+      </c>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="27" thickBot="1">
+      <c r="A8" s="44">
+        <v>4</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="40">
+        <v>8</v>
+      </c>
+      <c r="D8" s="46">
+        <v>9</v>
+      </c>
+      <c r="E8" s="46">
+        <v>1</v>
+      </c>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47">
+        <v>1</v>
+      </c>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46">
+        <v>1</v>
+      </c>
+      <c r="N8" s="46">
+        <v>0</v>
+      </c>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="27" thickBot="1">
+      <c r="A9" s="44">
+        <v>5</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="40">
+        <v>9</v>
+      </c>
+      <c r="D9" s="46">
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="46">
+        <v>1</v>
+      </c>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47">
+        <v>1</v>
+      </c>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46">
+        <v>1</v>
+      </c>
+      <c r="N9" s="46">
+        <v>0</v>
+      </c>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15" thickBot="1">
+      <c r="A10" s="44">
+        <v>6</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="40">
+        <v>72</v>
+      </c>
+      <c r="D10" s="46">
+        <v>2</v>
+      </c>
+      <c r="E10" s="46">
+        <v>1</v>
+      </c>
+      <c r="F10" s="46">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47">
+        <v>2</v>
+      </c>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46">
+        <v>1</v>
+      </c>
+      <c r="N10" s="46">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="27" thickBot="1">
+      <c r="A11" s="44">
+        <v>7</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="40">
+        <v>8</v>
+      </c>
+      <c r="D11" s="46">
+        <v>2</v>
+      </c>
+      <c r="E11" s="46">
+        <v>1</v>
+      </c>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47">
+        <v>1</v>
+      </c>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46">
+        <v>1</v>
+      </c>
+      <c r="N11" s="46">
+        <v>0</v>
+      </c>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="27" thickBot="1">
+      <c r="A12" s="44">
+        <v>8</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="40">
+        <v>36</v>
+      </c>
+      <c r="D12" s="46">
+        <v>2</v>
+      </c>
+      <c r="E12" s="46">
+        <v>1</v>
+      </c>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47">
+        <v>1</v>
+      </c>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46">
+        <v>1</v>
+      </c>
+      <c r="N12" s="46">
+        <v>0</v>
+      </c>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="27" thickBot="1">
+      <c r="A13" s="44">
+        <v>9</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="40">
+        <v>486</v>
+      </c>
+      <c r="D13" s="46">
+        <v>2</v>
+      </c>
+      <c r="E13" s="46">
+        <v>7</v>
+      </c>
+      <c r="F13" s="46">
+        <v>3</v>
+      </c>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47">
+        <v>10</v>
+      </c>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46">
+        <v>7</v>
+      </c>
+      <c r="N13" s="46">
+        <v>3</v>
+      </c>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15" thickBot="1">
+      <c r="A14" s="44">
+        <v>10</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="40">
+        <v>42</v>
+      </c>
+      <c r="D14" s="46">
+        <v>2</v>
+      </c>
+      <c r="E14" s="46">
+        <v>1</v>
+      </c>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47">
+        <v>1</v>
+      </c>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46">
+        <v>1</v>
+      </c>
+      <c r="N14" s="46">
+        <v>0</v>
+      </c>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="J1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F4D111-C1D1-4C62-9072-5C5E8256620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DC64B7-A19B-48E6-9851-6549BC9EFA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
     <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId3"/>
-    <sheet name="Trang_tính1" sheetId="10" r:id="rId4"/>
+    <sheet name="Trang_tính2" sheetId="11" r:id="rId4"/>
+    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="102">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -225,13 +229,144 @@
   </si>
   <si>
     <t>Súng tiểu liên</t>
+  </si>
+  <si>
+    <t>Nội dung, Đơn vị được vận chuyển</t>
+  </si>
+  <si>
+    <t>TBKT, vật chất HC, KT</t>
+  </si>
+  <si>
+    <t>Địa điểm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cự ly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(km)</t>
+    </r>
+  </si>
+  <si>
+    <t>Vận chuyển thô sơ</t>
+  </si>
+  <si>
+    <t>Vận chuyển khác</t>
+  </si>
+  <si>
+    <t>Chủng loại</t>
+  </si>
+  <si>
+    <t>Khối lượng (tấn)</t>
+  </si>
+  <si>
+    <t>Nơi nhận</t>
+  </si>
+  <si>
+    <t>Nơi giao</t>
+  </si>
+  <si>
+    <t>TBKT</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>vật chất (tấn)</t>
+  </si>
+  <si>
+    <t>Bắt đầu</t>
+  </si>
+  <si>
+    <t>Kết thúc</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ</t>
+  </si>
+  <si>
+    <t>GĐCB CĐ</t>
+  </si>
+  <si>
+    <t>QN</t>
+  </si>
+  <si>
+    <t>HCKT/d</t>
+  </si>
+  <si>
+    <t>Các hướng</t>
+  </si>
+  <si>
+    <t>17.00 N-3</t>
+  </si>
+  <si>
+    <t>20.00 N-3</t>
+  </si>
+  <si>
+    <t>QY</t>
+  </si>
+  <si>
+    <t>17.00 N-2</t>
+  </si>
+  <si>
+    <t>20.00 N-2</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>VTKT</t>
+  </si>
+  <si>
+    <t>Đạn</t>
+  </si>
+  <si>
+    <t>21.00 N-1</t>
+  </si>
+  <si>
+    <t>23.00 N-1</t>
+  </si>
+  <si>
+    <t>GĐTH CĐ</t>
+  </si>
+  <si>
+    <t>Khi có lệnh</t>
+  </si>
+  <si>
+    <t>Hướng CY</t>
+  </si>
+  <si>
+    <t>HCY</t>
+  </si>
+  <si>
+    <t>Hướng TY</t>
+  </si>
+  <si>
+    <t>HTY</t>
+  </si>
+  <si>
+    <t>LL dự bị</t>
+  </si>
+  <si>
+    <t>LLDB</t>
+  </si>
+  <si>
+    <t>LLCL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +438,19 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -614,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -641,15 +789,137 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -677,82 +947,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,6 +980,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="Giao diện"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1037,42 +1271,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="23"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="24"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1481,79 +1715,79 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="13" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="13" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="52" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
@@ -1859,102 +2093,102 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="13" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="13" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="61" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5">
@@ -2307,6 +2541,1635 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED79D5-2184-4663-817F-4F354B351A91}">
+  <dimension ref="A1:M60"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="36"/>
+      <c r="K3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="36"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+    </row>
+    <row r="6" spans="1:13" ht="27.6">
+      <c r="A6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="18">
+        <v>63</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+    </row>
+    <row r="7" spans="1:13" ht="27.6">
+      <c r="A7" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="36">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="e">
+        <f>D7</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+    </row>
+    <row r="8" spans="1:13" ht="27.6">
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="e">
+        <f t="shared" ref="H8:H60" si="0">D8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" spans="1:13" ht="27.6">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+    </row>
+    <row r="10" spans="1:13" ht="27.6">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+    </row>
+    <row r="11" spans="1:13" ht="27.6">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="37">
+        <v>63</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I16" s="27"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="27.6">
+      <c r="A17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="18">
+        <v>25</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="27.6">
+      <c r="A18" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="25">
+        <v>0.7</v>
+      </c>
+      <c r="H18" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="27.6">
+      <c r="A19" s="26"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="27.6">
+      <c r="A20" s="26"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="27.6">
+      <c r="A21" s="26"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="21" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" ht="27.6">
+      <c r="A22" s="27"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="21" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="28">
+        <v>25</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="25">
+        <v>1</v>
+      </c>
+      <c r="H23" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="26"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="26"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I25" s="26"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="26"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="26"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="27"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I27" s="27"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+    </row>
+    <row r="28" spans="1:13" ht="27.6">
+      <c r="A28" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="18">
+        <v>10</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+    </row>
+    <row r="29" spans="1:13" ht="27.6">
+      <c r="A29" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="25">
+        <v>1</v>
+      </c>
+      <c r="H29" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+    </row>
+    <row r="30" spans="1:13" ht="27.6">
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+    </row>
+    <row r="31" spans="1:13" ht="27.6">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" ht="27.6">
+      <c r="A32" s="34"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+    </row>
+    <row r="33" spans="1:13" ht="27.6">
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="H34" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I35" s="26"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="35"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I38" s="27"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="18">
+        <v>1</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+    </row>
+    <row r="40" spans="1:13" ht="27.6">
+      <c r="A40" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" s="28">
+        <v>0.7</v>
+      </c>
+      <c r="H40" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+    </row>
+    <row r="41" spans="1:13" ht="27.6">
+      <c r="A41" s="29"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+    </row>
+    <row r="42" spans="1:13" ht="27.6">
+      <c r="A42" s="29"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+    </row>
+    <row r="43" spans="1:13" ht="27.6">
+      <c r="A43" s="29"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="23"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" ht="27.6">
+      <c r="A44" s="30"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="25">
+        <v>1</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="H45" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I46" s="26"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I47" s="26"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="23"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="26"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I49" s="27"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+    </row>
+    <row r="50" spans="1:13" ht="27.6">
+      <c r="A50" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="18">
+        <v>25</v>
+      </c>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+    </row>
+    <row r="51" spans="1:13" ht="27.6">
+      <c r="A51" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+    </row>
+    <row r="52" spans="1:13" ht="27.6">
+      <c r="A52" s="26"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I52" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+    </row>
+    <row r="53" spans="1:13" ht="27.6">
+      <c r="A53" s="26"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I53" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+    </row>
+    <row r="54" spans="1:13" ht="27.6">
+      <c r="A54" s="26"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I54" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+    </row>
+    <row r="55" spans="1:13" ht="27.6">
+      <c r="A55" s="27"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I55" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="25">
+        <v>25</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G56" s="28">
+        <v>0.3</v>
+      </c>
+      <c r="H56" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="22"/>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I57" s="26"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I58" s="26"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="26"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D59" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I59" s="26"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="27"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I60" s="27"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="K1:M2"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="G1:G5"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="G18:G22"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="I23:I27"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="G23:G27"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G56:G60"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2315,500 +4178,500 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38" t="s">
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="38" t="s">
+      <c r="K1" s="65"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="66"/>
     </row>
     <row r="2" spans="1:17" ht="32.4" customHeight="1" thickBot="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="27" thickBot="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
     </row>
     <row r="4" spans="1:17" ht="27" thickBot="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
     </row>
     <row r="5" spans="1:17" ht="27" thickBot="1">
-      <c r="A5" s="44">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="10">
         <v>9</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="16">
         <v>8</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="16">
         <v>1</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="47">
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17">
         <v>1</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46">
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16">
         <v>1</v>
       </c>
-      <c r="N5" s="46">
-        <v>0</v>
-      </c>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46">
+      <c r="N5" s="16">
+        <v>0</v>
+      </c>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="27" thickBot="1">
-      <c r="A6" s="44">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="10">
         <v>4</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="16">
         <v>9</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="16">
         <v>1</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47">
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17">
         <v>1</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16">
         <v>1</v>
       </c>
-      <c r="N6" s="46">
-        <v>0</v>
-      </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46">
+      <c r="N6" s="16">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="27" thickBot="1">
-      <c r="A7" s="44">
+      <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="10">
         <v>4</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="16">
         <v>9</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="16">
         <v>1</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17">
         <v>1</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16">
         <v>1</v>
       </c>
-      <c r="N7" s="46">
-        <v>0</v>
-      </c>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46">
+      <c r="N7" s="16">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="27" thickBot="1">
-      <c r="A8" s="44">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="10">
         <v>8</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="16">
         <v>9</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="16">
         <v>1</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="47">
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17">
         <v>1</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16">
         <v>1</v>
       </c>
-      <c r="N8" s="46">
-        <v>0</v>
-      </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46">
+      <c r="N8" s="16">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="27" thickBot="1">
-      <c r="A9" s="44">
+      <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="10">
         <v>9</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="16">
         <v>7.5</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="16">
         <v>1</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17">
         <v>1</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16">
         <v>1</v>
       </c>
-      <c r="N9" s="46">
-        <v>0</v>
-      </c>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46">
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" thickBot="1">
-      <c r="A10" s="44">
+      <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="10">
         <v>72</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="16">
         <v>2</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="16">
         <v>1</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="16">
         <v>1</v>
       </c>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47">
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17">
         <v>2</v>
       </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46">
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16">
         <v>1</v>
       </c>
-      <c r="N10" s="46">
+      <c r="N10" s="16">
         <v>1</v>
       </c>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46">
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="27" thickBot="1">
-      <c r="A11" s="44">
+      <c r="A11" s="14">
         <v>7</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="10">
         <v>8</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="16">
         <v>2</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="16">
         <v>1</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17">
         <v>1</v>
       </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46">
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16">
         <v>1</v>
       </c>
-      <c r="N11" s="46">
-        <v>0</v>
-      </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46">
+      <c r="N11" s="16">
+        <v>0</v>
+      </c>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="27" thickBot="1">
-      <c r="A12" s="44">
+      <c r="A12" s="14">
         <v>8</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="10">
         <v>36</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="16">
         <v>2</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="16">
         <v>1</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17">
         <v>1</v>
       </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46">
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16">
         <v>1</v>
       </c>
-      <c r="N12" s="46">
-        <v>0</v>
-      </c>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46">
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="27" thickBot="1">
-      <c r="A13" s="44">
+      <c r="A13" s="14">
         <v>9</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="10">
         <v>486</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="16">
         <v>2</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="16">
         <v>7</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="16">
         <v>3</v>
       </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47">
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17">
         <v>10</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46">
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16">
         <v>7</v>
       </c>
-      <c r="N13" s="46">
+      <c r="N13" s="16">
         <v>3</v>
       </c>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46">
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" thickBot="1">
-      <c r="A14" s="44">
+      <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="10">
         <v>42</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="16">
         <v>2</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="16">
         <v>1</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47">
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17">
         <v>1</v>
       </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46">
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16">
         <v>1</v>
       </c>
-      <c r="N14" s="46">
-        <v>0</v>
-      </c>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46">
+      <c r="N14" s="16">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16">
         <v>1</v>
       </c>
     </row>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -5,22 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DC64B7-A19B-48E6-9851-6549BC9EFA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514FFB9C-324A-44A2-BD01-8B4EDE8BBA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
     <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId3"/>
     <sheet name="Trang_tính2" sheetId="11" r:id="rId4"/>
-    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId5"/>
+    <sheet name="KeHoach9.2" sheetId="12" r:id="rId5"/>
+    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="119">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -358,15 +360,67 @@
   <si>
     <t>LLCL</t>
   </si>
+  <si>
+    <t>Khối lượng vận chuyển</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Vũ khí trang bị kỹ thuật</t>
+  </si>
+  <si>
+    <t>Vật chất hậu cần</t>
+  </si>
+  <si>
+    <t>Vật chất khác</t>
+  </si>
+  <si>
+    <t>Cộng</t>
+  </si>
+  <si>
+    <t>VKTB</t>
+  </si>
+  <si>
+    <t>XD</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t>tấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tấn </t>
+  </si>
+  <si>
+    <t>người</t>
+  </si>
+  <si>
+    <t>GĐCB</t>
+  </si>
+  <si>
+    <t>Trên chuyển</t>
+  </si>
+  <si>
+    <t>Cấp mình</t>
+  </si>
+  <si>
+    <t>Dưới chuyển</t>
+  </si>
+  <si>
+    <t>GĐCĐ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,6 +504,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -762,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -830,6 +891,90 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -840,15 +985,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -866,87 +1002,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -964,6 +1028,52 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,6 +1109,64 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="Giao diện"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="10">
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>1.25</v>
+          </cell>
+          <cell r="E11">
+            <v>1.25</v>
+          </cell>
+          <cell r="H11">
+            <v>1.5</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>1.25</v>
+          </cell>
+          <cell r="E16">
+            <v>1.25</v>
+          </cell>
+          <cell r="H16">
+            <v>1.5</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
     </sheetDataSet>
@@ -1265,48 +1433,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AC3B-8D90-4B0D-96EA-52FB68143200}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="48"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="41"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="42"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1712,82 +1880,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C04A3E4-2F16-400C-90BF-200CB05E84C8}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="55" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="38" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="52" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="53"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
@@ -2090,105 +2258,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC69830-15C2-40EF-A85C-0B734C645A25}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="58" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="46"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="55" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="L2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="52" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="53"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5">
@@ -2543,126 +2711,126 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED79D5-2184-4663-817F-4F354B351A91}">
   <dimension ref="A1:M60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="62"/>
+      <c r="E1" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38" t="s">
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38" t="s">
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="38"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="38"/>
+      <c r="G3" s="62"/>
       <c r="H3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="36"/>
+      <c r="J3" s="61"/>
       <c r="K3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="36"/>
+      <c r="M3" s="61"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="36" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="61" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-    </row>
-    <row r="6" spans="1:13" ht="27.6">
+      <c r="A5" s="62"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+    </row>
+    <row r="6" spans="1:13" ht="28.5">
       <c r="A6" s="19" t="s">
         <v>78</v>
       </c>
@@ -2681,11 +2849,11 @@
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="1:13" ht="27.6">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:13" ht="30">
+      <c r="A7" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="61">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -2695,13 +2863,13 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="53"/>
       <c r="H7" s="21" t="e">
         <f>D7</f>
         <v>#REF!</v>
@@ -2716,9 +2884,9 @@
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
     </row>
-    <row r="8" spans="1:13" ht="27.6">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36"/>
+    <row r="8" spans="1:13" ht="30">
+      <c r="A8" s="61"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="20" t="s">
         <v>85</v>
       </c>
@@ -2726,9 +2894,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
       <c r="H8" s="21" t="e">
         <f t="shared" ref="H8:H60" si="0">D8</f>
         <v>#REF!</v>
@@ -2743,9 +2911,9 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="1:13" ht="27.6">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="20" t="s">
         <v>88</v>
       </c>
@@ -2753,9 +2921,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
       <c r="H9" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -2770,9 +2938,9 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
     </row>
-    <row r="10" spans="1:13" ht="27.6">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+    <row r="10" spans="1:13" ht="30">
+      <c r="A10" s="61"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="22" t="s">
         <v>89</v>
       </c>
@@ -2780,9 +2948,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -2797,9 +2965,9 @@
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" spans="1:13" ht="27.6">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
+    <row r="11" spans="1:13" ht="30">
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="20" t="s">
         <v>90</v>
       </c>
@@ -2807,9 +2975,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
       <c r="H11" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -2825,10 +2993,10 @@
       <c r="M11" s="20"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="64">
         <v>63</v>
       </c>
       <c r="C12" s="20" t="s">
@@ -2838,18 +3006,18 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="53" t="s">
         <v>94</v>
       </c>
       <c r="J12" s="20"/>
@@ -2858,8 +3026,8 @@
       <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="36"/>
-      <c r="B13" s="37"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="20" t="s">
         <v>85</v>
       </c>
@@ -2867,22 +3035,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I13" s="26"/>
+      <c r="I13" s="54"/>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="64"/>
       <c r="C14" s="20" t="s">
         <v>88</v>
       </c>
@@ -2890,22 +3058,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
       <c r="H14" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="54"/>
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="22" t="s">
         <v>89</v>
       </c>
@@ -2913,22 +3081,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
       <c r="H15" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I15" s="26"/>
+      <c r="I15" s="54"/>
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
       <c r="L15" s="20"/>
       <c r="M15" s="20"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="64"/>
       <c r="C16" s="20" t="s">
         <v>90</v>
       </c>
@@ -2936,20 +3104,20 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
       <c r="H16" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I16" s="27"/>
+      <c r="I16" s="55"/>
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
     </row>
-    <row r="17" spans="1:13" ht="27.6">
+    <row r="17" spans="1:13" ht="28.5">
       <c r="A17" s="19" t="s">
         <v>95</v>
       </c>
@@ -2968,11 +3136,11 @@
       <c r="L17" s="20"/>
       <c r="M17" s="20"/>
     </row>
-    <row r="18" spans="1:13" ht="27.6">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:13" ht="30">
+      <c r="A18" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="31"/>
+      <c r="B18" s="56"/>
       <c r="C18" s="20" t="s">
         <v>80</v>
       </c>
@@ -2980,13 +3148,13 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="53">
         <v>0.7</v>
       </c>
       <c r="H18" s="21" t="e">
@@ -3003,9 +3171,9 @@
       <c r="L18" s="20"/>
       <c r="M18" s="20"/>
     </row>
-    <row r="19" spans="1:13" ht="27.6">
-      <c r="A19" s="26"/>
-      <c r="B19" s="32"/>
+    <row r="19" spans="1:13" ht="30">
+      <c r="A19" s="54"/>
+      <c r="B19" s="57"/>
       <c r="C19" s="20" t="s">
         <v>85</v>
       </c>
@@ -3013,9 +3181,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
       <c r="H19" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3030,9 +3198,9 @@
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
     </row>
-    <row r="20" spans="1:13" ht="27.6">
-      <c r="A20" s="26"/>
-      <c r="B20" s="32"/>
+    <row r="20" spans="1:13" ht="30">
+      <c r="A20" s="54"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="20" t="s">
         <v>88</v>
       </c>
@@ -3040,9 +3208,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
       <c r="H20" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3057,9 +3225,9 @@
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
     </row>
-    <row r="21" spans="1:13" ht="27.6">
-      <c r="A21" s="26"/>
-      <c r="B21" s="32"/>
+    <row r="21" spans="1:13" ht="30">
+      <c r="A21" s="54"/>
+      <c r="B21" s="57"/>
       <c r="C21" s="22" t="s">
         <v>89</v>
       </c>
@@ -3067,9 +3235,9 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
       <c r="H21" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3084,9 +3252,9 @@
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
     </row>
-    <row r="22" spans="1:13" ht="27.6">
-      <c r="A22" s="27"/>
-      <c r="B22" s="33"/>
+    <row r="22" spans="1:13" ht="30">
+      <c r="A22" s="55"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="20" t="s">
         <v>90</v>
       </c>
@@ -3094,9 +3262,9 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
       <c r="H22" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3112,10 +3280,10 @@
       <c r="M22" s="20"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="50">
         <v>25</v>
       </c>
       <c r="C23" s="20" t="s">
@@ -3125,20 +3293,20 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="53">
         <v>1</v>
       </c>
       <c r="H23" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I23" s="25" t="s">
+      <c r="I23" s="53" t="s">
         <v>94</v>
       </c>
       <c r="J23" s="20"/>
@@ -3147,8 +3315,8 @@
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="26"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="51"/>
       <c r="C24" s="20" t="s">
         <v>85</v>
       </c>
@@ -3156,22 +3324,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
       <c r="H24" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I24" s="26"/>
+      <c r="I24" s="54"/>
       <c r="J24" s="20"/>
       <c r="K24" s="20"/>
       <c r="L24" s="20"/>
       <c r="M24" s="20"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="26"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="51"/>
       <c r="C25" s="20" t="s">
         <v>88</v>
       </c>
@@ -3179,42 +3347,42 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
       <c r="H25" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I25" s="26"/>
+      <c r="I25" s="54"/>
       <c r="J25" s="20"/>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="26"/>
-      <c r="B26" s="29"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="51"/>
       <c r="C26" s="22" t="s">
         <v>89</v>
       </c>
       <c r="D26" s="21"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
       <c r="H26" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="26"/>
+      <c r="I26" s="54"/>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="27"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="20" t="s">
         <v>90</v>
       </c>
@@ -3222,20 +3390,20 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
       <c r="H27" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I27" s="27"/>
+      <c r="I27" s="55"/>
       <c r="J27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
       <c r="M27" s="22"/>
     </row>
-    <row r="28" spans="1:13" ht="27.6">
+    <row r="28" spans="1:13" ht="28.5">
       <c r="A28" s="19" t="s">
         <v>97</v>
       </c>
@@ -3254,11 +3422,11 @@
       <c r="L28" s="22"/>
       <c r="M28" s="22"/>
     </row>
-    <row r="29" spans="1:13" ht="27.6">
-      <c r="A29" s="28" t="s">
+    <row r="29" spans="1:13" ht="30">
+      <c r="A29" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="50"/>
       <c r="C29" s="20" t="s">
         <v>80</v>
       </c>
@@ -3266,13 +3434,13 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="53">
         <v>1</v>
       </c>
       <c r="H29" s="21" t="e">
@@ -3289,9 +3457,9 @@
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
     </row>
-    <row r="30" spans="1:13" ht="27.6">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
+    <row r="30" spans="1:13" ht="30">
+      <c r="A30" s="59"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="20" t="s">
         <v>85</v>
       </c>
@@ -3299,9 +3467,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
       <c r="H30" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3316,9 +3484,9 @@
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
     </row>
-    <row r="31" spans="1:13" ht="27.6">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
+    <row r="31" spans="1:13" ht="30">
+      <c r="A31" s="59"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="20" t="s">
         <v>88</v>
       </c>
@@ -3326,9 +3494,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
       <c r="H31" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3343,16 +3511,16 @@
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
     </row>
-    <row r="32" spans="1:13" ht="27.6">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
+    <row r="32" spans="1:13" ht="30">
+      <c r="A32" s="59"/>
+      <c r="B32" s="59"/>
       <c r="C32" s="22" t="s">
         <v>89</v>
       </c>
       <c r="D32" s="23"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
       <c r="H32" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3367,9 +3535,9 @@
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="1:13" ht="27.6">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35"/>
+    <row r="33" spans="1:13" ht="30">
+      <c r="A33" s="60"/>
+      <c r="B33" s="60"/>
       <c r="C33" s="20" t="s">
         <v>90</v>
       </c>
@@ -3377,9 +3545,9 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
       <c r="H33" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3395,10 +3563,10 @@
       <c r="M33" s="22"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="28"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="20" t="s">
         <v>80</v>
       </c>
@@ -3406,20 +3574,20 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="F34" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="50">
         <v>1.5</v>
       </c>
       <c r="H34" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I34" s="25" t="s">
+      <c r="I34" s="53" t="s">
         <v>94</v>
       </c>
       <c r="J34" s="22"/>
@@ -3428,8 +3596,8 @@
       <c r="M34" s="22"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
       <c r="C35" s="20" t="s">
         <v>85</v>
       </c>
@@ -3437,22 +3605,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="29"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="51"/>
       <c r="H35" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I35" s="26"/>
+      <c r="I35" s="54"/>
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="20" t="s">
         <v>88</v>
       </c>
@@ -3460,42 +3628,42 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="29"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="51"/>
       <c r="H36" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I36" s="26"/>
+      <c r="I36" s="54"/>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="22" t="s">
         <v>89</v>
       </c>
       <c r="D37" s="23"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="29"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="51"/>
       <c r="H37" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="26"/>
+      <c r="I37" s="54"/>
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
       <c r="M37" s="22"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="35"/>
-      <c r="B38" s="35"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="60"/>
       <c r="C38" s="20" t="s">
         <v>90</v>
       </c>
@@ -3503,14 +3671,14 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="30"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="52"/>
       <c r="H38" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I38" s="27"/>
+      <c r="I38" s="55"/>
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
@@ -3535,11 +3703,11 @@
       <c r="L39" s="22"/>
       <c r="M39" s="22"/>
     </row>
-    <row r="40" spans="1:13" ht="27.6">
-      <c r="A40" s="28" t="s">
+    <row r="40" spans="1:13" ht="30">
+      <c r="A40" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="31"/>
+      <c r="B40" s="56"/>
       <c r="C40" s="20" t="s">
         <v>80</v>
       </c>
@@ -3547,13 +3715,13 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="50">
         <v>0.7</v>
       </c>
       <c r="H40" s="21" t="e">
@@ -3570,9 +3738,9 @@
       <c r="L40" s="22"/>
       <c r="M40" s="22"/>
     </row>
-    <row r="41" spans="1:13" ht="27.6">
-      <c r="A41" s="29"/>
-      <c r="B41" s="32"/>
+    <row r="41" spans="1:13" ht="30">
+      <c r="A41" s="51"/>
+      <c r="B41" s="57"/>
       <c r="C41" s="20" t="s">
         <v>85</v>
       </c>
@@ -3580,9 +3748,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="29"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="51"/>
       <c r="H41" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3597,9 +3765,9 @@
       <c r="L41" s="22"/>
       <c r="M41" s="22"/>
     </row>
-    <row r="42" spans="1:13" ht="27.6">
-      <c r="A42" s="29"/>
-      <c r="B42" s="32"/>
+    <row r="42" spans="1:13" ht="30">
+      <c r="A42" s="51"/>
+      <c r="B42" s="57"/>
       <c r="C42" s="20" t="s">
         <v>88</v>
       </c>
@@ -3607,9 +3775,9 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="29"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="51"/>
       <c r="H42" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3624,16 +3792,16 @@
       <c r="L42" s="22"/>
       <c r="M42" s="22"/>
     </row>
-    <row r="43" spans="1:13" ht="27.6">
-      <c r="A43" s="29"/>
-      <c r="B43" s="32"/>
+    <row r="43" spans="1:13" ht="30">
+      <c r="A43" s="51"/>
+      <c r="B43" s="57"/>
       <c r="C43" s="22" t="s">
         <v>89</v>
       </c>
       <c r="D43" s="23"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="29"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="51"/>
       <c r="H43" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3648,9 +3816,9 @@
       <c r="L43" s="22"/>
       <c r="M43" s="22"/>
     </row>
-    <row r="44" spans="1:13" ht="27.6">
-      <c r="A44" s="30"/>
-      <c r="B44" s="33"/>
+    <row r="44" spans="1:13" ht="30">
+      <c r="A44" s="52"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="20" t="s">
         <v>90</v>
       </c>
@@ -3658,9 +3826,9 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="30"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="52"/>
       <c r="H44" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3676,10 +3844,10 @@
       <c r="M44" s="22"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="53">
         <v>1</v>
       </c>
       <c r="C45" s="20" t="s">
@@ -3689,20 +3857,20 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F45" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="50">
         <v>0.8</v>
       </c>
       <c r="H45" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I45" s="25" t="s">
+      <c r="I45" s="53" t="s">
         <v>94</v>
       </c>
       <c r="J45" s="22"/>
@@ -3711,8 +3879,8 @@
       <c r="M45" s="22"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26"/>
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="20" t="s">
         <v>85</v>
       </c>
@@ -3720,22 +3888,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="29"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="51"/>
       <c r="H46" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I46" s="26"/>
+      <c r="I46" s="54"/>
       <c r="J46" s="22"/>
       <c r="K46" s="22"/>
       <c r="L46" s="22"/>
       <c r="M46" s="22"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="20" t="s">
         <v>88</v>
       </c>
@@ -3743,42 +3911,42 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="29"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="51"/>
       <c r="H47" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I47" s="26"/>
+      <c r="I47" s="54"/>
       <c r="J47" s="22"/>
       <c r="K47" s="22"/>
       <c r="L47" s="22"/>
       <c r="M47" s="22"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
       <c r="C48" s="22" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="23"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="29"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="51"/>
       <c r="H48" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I48" s="26"/>
+      <c r="I48" s="54"/>
       <c r="J48" s="22"/>
       <c r="K48" s="22"/>
       <c r="L48" s="22"/>
       <c r="M48" s="22"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
+      <c r="A49" s="55"/>
+      <c r="B49" s="55"/>
       <c r="C49" s="20" t="s">
         <v>90</v>
       </c>
@@ -3786,20 +3954,20 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="30"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="52"/>
       <c r="H49" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I49" s="27"/>
+      <c r="I49" s="55"/>
       <c r="J49" s="22"/>
       <c r="K49" s="22"/>
       <c r="L49" s="22"/>
       <c r="M49" s="22"/>
     </row>
-    <row r="50" spans="1:13" ht="27.6">
+    <row r="50" spans="1:13" ht="28.5">
       <c r="A50" s="19" t="s">
         <v>38</v>
       </c>
@@ -3818,11 +3986,11 @@
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
     </row>
-    <row r="51" spans="1:13" ht="27.6">
-      <c r="A51" s="25" t="s">
+    <row r="51" spans="1:13" ht="30">
+      <c r="A51" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="31"/>
+      <c r="B51" s="56"/>
       <c r="C51" s="20" t="s">
         <v>80</v>
       </c>
@@ -3830,13 +3998,13 @@
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="28">
+      <c r="G51" s="50">
         <v>0.5</v>
       </c>
       <c r="H51" s="21" t="e">
@@ -3853,9 +4021,9 @@
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
     </row>
-    <row r="52" spans="1:13" ht="27.6">
-      <c r="A52" s="26"/>
-      <c r="B52" s="32"/>
+    <row r="52" spans="1:13" ht="30">
+      <c r="A52" s="54"/>
+      <c r="B52" s="57"/>
       <c r="C52" s="20" t="s">
         <v>85</v>
       </c>
@@ -3863,9 +4031,9 @@
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="29"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="51"/>
       <c r="H52" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3880,9 +4048,9 @@
       <c r="L52" s="22"/>
       <c r="M52" s="22"/>
     </row>
-    <row r="53" spans="1:13" ht="27.6">
-      <c r="A53" s="26"/>
-      <c r="B53" s="32"/>
+    <row r="53" spans="1:13" ht="30">
+      <c r="A53" s="54"/>
+      <c r="B53" s="57"/>
       <c r="C53" s="20" t="s">
         <v>88</v>
       </c>
@@ -3890,9 +4058,9 @@
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="29"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="51"/>
       <c r="H53" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3907,9 +4075,9 @@
       <c r="L53" s="22"/>
       <c r="M53" s="22"/>
     </row>
-    <row r="54" spans="1:13" ht="27.6">
-      <c r="A54" s="26"/>
-      <c r="B54" s="32"/>
+    <row r="54" spans="1:13" ht="30">
+      <c r="A54" s="54"/>
+      <c r="B54" s="57"/>
       <c r="C54" s="22" t="s">
         <v>89</v>
       </c>
@@ -3917,9 +4085,9 @@
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="29"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="51"/>
       <c r="H54" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3934,9 +4102,9 @@
       <c r="L54" s="22"/>
       <c r="M54" s="22"/>
     </row>
-    <row r="55" spans="1:13" ht="27.6">
-      <c r="A55" s="27"/>
-      <c r="B55" s="33"/>
+    <row r="55" spans="1:13" ht="30">
+      <c r="A55" s="55"/>
+      <c r="B55" s="58"/>
       <c r="C55" s="20" t="s">
         <v>90</v>
       </c>
@@ -3944,9 +4112,9 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="30"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="52"/>
       <c r="H55" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -3962,10 +4130,10 @@
       <c r="M55" s="22"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="53">
         <v>25</v>
       </c>
       <c r="C56" s="20" t="s">
@@ -3975,20 +4143,20 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E56" s="25" t="s">
+      <c r="E56" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F56" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="G56" s="28">
+      <c r="G56" s="50">
         <v>0.3</v>
       </c>
       <c r="H56" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I56" s="25" t="s">
+      <c r="I56" s="53" t="s">
         <v>94</v>
       </c>
       <c r="J56" s="22"/>
@@ -3997,8 +4165,8 @@
       <c r="M56" s="22"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="26"/>
-      <c r="B57" s="26"/>
+      <c r="A57" s="54"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="20" t="s">
         <v>85</v>
       </c>
@@ -4006,22 +4174,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="29"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="51"/>
       <c r="H57" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I57" s="26"/>
+      <c r="I57" s="54"/>
       <c r="J57" s="22"/>
       <c r="K57" s="22"/>
       <c r="L57" s="22"/>
       <c r="M57" s="22"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26"/>
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
       <c r="C58" s="20" t="s">
         <v>88</v>
       </c>
@@ -4029,22 +4197,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="29"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="51"/>
       <c r="H58" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I58" s="26"/>
+      <c r="I58" s="54"/>
       <c r="J58" s="22"/>
       <c r="K58" s="22"/>
       <c r="L58" s="22"/>
       <c r="M58" s="22"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="26"/>
-      <c r="B59" s="26"/>
+      <c r="A59" s="54"/>
+      <c r="B59" s="54"/>
       <c r="C59" s="22" t="s">
         <v>89</v>
       </c>
@@ -4052,22 +4220,22 @@
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="29"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="51"/>
       <c r="H59" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I59" s="26"/>
+      <c r="I59" s="54"/>
       <c r="J59" s="22"/>
       <c r="K59" s="22"/>
       <c r="L59" s="22"/>
       <c r="M59" s="22"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="27"/>
-      <c r="B60" s="27"/>
+      <c r="A60" s="55"/>
+      <c r="B60" s="55"/>
       <c r="C60" s="20" t="s">
         <v>90</v>
       </c>
@@ -4075,14 +4243,14 @@
         <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="30"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="52"/>
       <c r="H60" s="21" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I60" s="27"/>
+      <c r="I60" s="55"/>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
       <c r="L60" s="22"/>
@@ -4141,12 +4309,14 @@
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="E34:E38"/>
     <mergeCell ref="F34:F38"/>
+    <mergeCell ref="F56:F60"/>
     <mergeCell ref="G34:G38"/>
     <mergeCell ref="A40:A44"/>
     <mergeCell ref="B40:B44"/>
     <mergeCell ref="E40:E44"/>
     <mergeCell ref="F40:F44"/>
     <mergeCell ref="G40:G44"/>
+    <mergeCell ref="G56:G60"/>
     <mergeCell ref="I56:I60"/>
     <mergeCell ref="I45:I49"/>
     <mergeCell ref="A51:A55"/>
@@ -4162,59 +4332,540 @@
     <mergeCell ref="A56:A60"/>
     <mergeCell ref="B56:B60"/>
     <mergeCell ref="E56:E60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="G56:G60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5507F-02BA-4790-AB88-8656D327FB49}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="71" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="75"/>
+      <c r="B2" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="75"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="76"/>
+      <c r="B3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+    </row>
+    <row r="4" spans="1:14" ht="25.5">
+      <c r="A4" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="L4" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="M4" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="N4" s="77"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80">
+        <f>C6+C10</f>
+        <v>8</v>
+      </c>
+      <c r="D5" s="80" t="e">
+        <f>(D6+D10)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="80" t="e">
+        <f t="shared" ref="E5:J5" si="0">E6+E10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K5" s="79"/>
+      <c r="L5" s="80" t="e">
+        <f>E5+J5</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M5" s="81">
+        <v>63</v>
+      </c>
+      <c r="N5" s="79"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80">
+        <f>C7+C8+C9</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="80" t="e">
+        <f>(D7+D8+D9)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="80" t="e">
+        <f t="shared" ref="E6:I6" si="1">E7+E8+E9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F6" s="80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J6" s="80" t="e">
+        <f>F6+G6+H6+I6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K6" s="79"/>
+      <c r="L6" s="80" t="e">
+        <f t="shared" ref="L6:L13" si="2">E6+J6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+    </row>
+    <row r="7" spans="1:14" ht="30">
+      <c r="A7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80">
+        <f>[2]Đạn!B10+[2]Đạn!E10+[2]Đạn!B11+[2]Đạn!E11</f>
+        <v>2.5</v>
+      </c>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80">
+        <f>B7+C7+D7</f>
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80">
+        <f t="shared" ref="J7:J13" si="3">F7+G7+H7+I7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="79"/>
+      <c r="L7" s="80">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="79"/>
+      <c r="C8" s="82">
+        <f>[2]Đạn!B16+[2]Đạn!E16+[2]Đạn!B22+[2]Đạn!E22</f>
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="82" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="82" t="e">
+        <f>B8+C8+D8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J8" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K8" s="79"/>
+      <c r="L8" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+    </row>
+    <row r="9" spans="1:14" ht="30">
+      <c r="A9" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80">
+        <f>B9+C9+D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="79"/>
+      <c r="L9" s="80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="79"/>
+      <c r="C10" s="80">
+        <f>C11+C12+C13</f>
+        <v>3</v>
+      </c>
+      <c r="D10" s="80" t="e">
+        <f>(D11+D12+D13)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="80" t="e">
+        <f t="shared" ref="E10:I10" si="4">E11+E12+E13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F10" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J10" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K10" s="79"/>
+      <c r="L10" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M10" s="81">
+        <v>63</v>
+      </c>
+      <c r="N10" s="79"/>
+    </row>
+    <row r="11" spans="1:14" ht="30">
+      <c r="A11" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80">
+        <f>[2]Đạn!H10+[2]Đạn!H11</f>
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="83"/>
+      <c r="E11" s="80">
+        <f>B11+C11+D11</f>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="79"/>
+      <c r="L11" s="80">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="84"/>
+      <c r="C12" s="85">
+        <f>[2]Đạn!H16+[2]Đạn!H22</f>
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="80" t="e">
+        <f t="shared" ref="E12:E13" si="5">B12+C12+D12</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J12" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K12" s="84"/>
+      <c r="L12" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M12" s="84">
+        <v>63</v>
+      </c>
+      <c r="N12" s="84"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="84" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="86"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="80">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="84"/>
+      <c r="L13" s="80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="9" width="8.88671875" customWidth="1"/>
+    <col min="5" max="9" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="64" t="s">
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="65"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="64" t="s">
+      <c r="K1" s="66"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="66"/>
-    </row>
-    <row r="2" spans="1:17" ht="32.4" customHeight="1" thickBot="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="67"/>
+    </row>
+    <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
       <c r="E2" s="10" t="s">
         <v>48</v>
       </c>
@@ -4255,7 +4906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="27" thickBot="1">
+    <row r="3" spans="1:17" ht="26.25" thickBot="1">
       <c r="A3" s="11" t="s">
         <v>50</v>
       </c>
@@ -4278,7 +4929,7 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
     </row>
-    <row r="4" spans="1:17" ht="27" thickBot="1">
+    <row r="4" spans="1:17" ht="26.25" thickBot="1">
       <c r="A4" s="11" t="s">
         <v>52</v>
       </c>
@@ -4301,7 +4952,7 @@
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
     </row>
-    <row r="5" spans="1:17" ht="27" thickBot="1">
+    <row r="5" spans="1:17" ht="26.25" thickBot="1">
       <c r="A5" s="14">
         <v>1</v>
       </c>
@@ -4338,7 +4989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="27" thickBot="1">
+    <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" s="14">
         <v>2</v>
       </c>
@@ -4375,7 +5026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="27" thickBot="1">
+    <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="14">
         <v>3</v>
       </c>
@@ -4412,7 +5063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="27" thickBot="1">
+    <row r="8" spans="1:17" ht="15.75" thickBot="1">
       <c r="A8" s="14">
         <v>4</v>
       </c>
@@ -4449,7 +5100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="27" thickBot="1">
+    <row r="9" spans="1:17" ht="26.25" thickBot="1">
       <c r="A9" s="14">
         <v>5</v>
       </c>
@@ -4486,7 +5137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1">
+    <row r="10" spans="1:17" ht="15.75" thickBot="1">
       <c r="A10" s="14">
         <v>6</v>
       </c>
@@ -4525,7 +5176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="27" thickBot="1">
+    <row r="11" spans="1:17" ht="26.25" thickBot="1">
       <c r="A11" s="14">
         <v>7</v>
       </c>
@@ -4562,7 +5213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="27" thickBot="1">
+    <row r="12" spans="1:17" ht="26.25" thickBot="1">
       <c r="A12" s="14">
         <v>8</v>
       </c>
@@ -4599,7 +5250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="27" thickBot="1">
+    <row r="13" spans="1:17" ht="26.25" thickBot="1">
       <c r="A13" s="14">
         <v>9</v>
       </c>
@@ -4638,7 +5289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" thickBot="1">
+    <row r="14" spans="1:17" ht="26.25" thickBot="1">
       <c r="A14" s="14">
         <v>10</v>
       </c>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F4D111-C1D1-4C62-9072-5C5E8256620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514FFB9C-324A-44A2-BD01-8B4EDE8BBA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
     <sheet name="BaoDamQuanY" sheetId="8" r:id="rId2"/>
     <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId3"/>
-    <sheet name="Trang_tính1" sheetId="10" r:id="rId4"/>
+    <sheet name="Trang_tính2" sheetId="11" r:id="rId4"/>
+    <sheet name="KeHoach9.2" sheetId="12" r:id="rId5"/>
+    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="119">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -225,13 +231,196 @@
   </si>
   <si>
     <t>Súng tiểu liên</t>
+  </si>
+  <si>
+    <t>Nội dung, Đơn vị được vận chuyển</t>
+  </si>
+  <si>
+    <t>TBKT, vật chất HC, KT</t>
+  </si>
+  <si>
+    <t>Địa điểm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cự ly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(km)</t>
+    </r>
+  </si>
+  <si>
+    <t>Vận chuyển thô sơ</t>
+  </si>
+  <si>
+    <t>Vận chuyển khác</t>
+  </si>
+  <si>
+    <t>Chủng loại</t>
+  </si>
+  <si>
+    <t>Khối lượng (tấn)</t>
+  </si>
+  <si>
+    <t>Nơi nhận</t>
+  </si>
+  <si>
+    <t>Nơi giao</t>
+  </si>
+  <si>
+    <t>TBKT</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>vật chất (tấn)</t>
+  </si>
+  <si>
+    <t>Bắt đầu</t>
+  </si>
+  <si>
+    <t>Kết thúc</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ</t>
+  </si>
+  <si>
+    <t>GĐCB CĐ</t>
+  </si>
+  <si>
+    <t>QN</t>
+  </si>
+  <si>
+    <t>HCKT/d</t>
+  </si>
+  <si>
+    <t>Các hướng</t>
+  </si>
+  <si>
+    <t>17.00 N-3</t>
+  </si>
+  <si>
+    <t>20.00 N-3</t>
+  </si>
+  <si>
+    <t>QY</t>
+  </si>
+  <si>
+    <t>17.00 N-2</t>
+  </si>
+  <si>
+    <t>20.00 N-2</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>VTKT</t>
+  </si>
+  <si>
+    <t>Đạn</t>
+  </si>
+  <si>
+    <t>21.00 N-1</t>
+  </si>
+  <si>
+    <t>23.00 N-1</t>
+  </si>
+  <si>
+    <t>GĐTH CĐ</t>
+  </si>
+  <si>
+    <t>Khi có lệnh</t>
+  </si>
+  <si>
+    <t>Hướng CY</t>
+  </si>
+  <si>
+    <t>HCY</t>
+  </si>
+  <si>
+    <t>Hướng TY</t>
+  </si>
+  <si>
+    <t>HTY</t>
+  </si>
+  <si>
+    <t>LL dự bị</t>
+  </si>
+  <si>
+    <t>LLDB</t>
+  </si>
+  <si>
+    <t>LLCL</t>
+  </si>
+  <si>
+    <t>Khối lượng vận chuyển</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Vũ khí trang bị kỹ thuật</t>
+  </si>
+  <si>
+    <t>Vật chất hậu cần</t>
+  </si>
+  <si>
+    <t>Vật chất khác</t>
+  </si>
+  <si>
+    <t>Cộng</t>
+  </si>
+  <si>
+    <t>VKTB</t>
+  </si>
+  <si>
+    <t>XD</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t>tấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tấn </t>
+  </si>
+  <si>
+    <t>người</t>
+  </si>
+  <si>
+    <t>GĐCB</t>
+  </si>
+  <si>
+    <t>Trên chuyển</t>
+  </si>
+  <si>
+    <t>Cấp mình</t>
+  </si>
+  <si>
+    <t>Dưới chuyển</t>
+  </si>
+  <si>
+    <t>GĐCĐ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +492,26 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -614,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -641,15 +850,95 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -677,83 +966,114 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -770,6 +1090,88 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="Giao diện"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="Giao diện"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="10">
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>1.25</v>
+          </cell>
+          <cell r="E11">
+            <v>1.25</v>
+          </cell>
+          <cell r="H11">
+            <v>1.5</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>1.25</v>
+          </cell>
+          <cell r="E16">
+            <v>1.25</v>
+          </cell>
+          <cell r="H16">
+            <v>1.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1031,48 +1433,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AC3B-8D90-4B0D-96EA-52FB68143200}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="23"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="24"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,82 +1880,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C04A3E4-2F16-400C-90BF-200CB05E84C8}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="13" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="13" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="38" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
@@ -1856,105 +2258,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC69830-15C2-40EF-A85C-0B734C645A25}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="46"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="13" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="13" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5">
@@ -2307,508 +2709,2620 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED79D5-2184-4663-817F-4F354B351A91}">
+  <dimension ref="A1:M60"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="62"/>
+      <c r="H3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="61"/>
+      <c r="K3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="61"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="62"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+    </row>
+    <row r="6" spans="1:13" ht="28.5">
+      <c r="A6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="18">
+        <v>63</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+    </row>
+    <row r="7" spans="1:13" ht="30">
+      <c r="A7" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="61">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="53"/>
+      <c r="H7" s="21" t="e">
+        <f>D7</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+    </row>
+    <row r="8" spans="1:13" ht="30">
+      <c r="A8" s="61"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="21" t="e">
+        <f t="shared" ref="H8:H60" si="0">D8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+    </row>
+    <row r="10" spans="1:13" ht="30">
+      <c r="A10" s="61"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+    </row>
+    <row r="11" spans="1:13" ht="30">
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="64">
+        <v>63</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="61"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I13" s="54"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="61"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I14" s="54"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="61"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I15" s="54"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="61"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I16" s="55"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="28.5">
+      <c r="A17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="18">
+        <v>25</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="30">
+      <c r="A18" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="53">
+        <v>0.7</v>
+      </c>
+      <c r="H18" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="30">
+      <c r="A19" s="54"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="30">
+      <c r="A20" s="54"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="30">
+      <c r="A21" s="54"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="21" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+    </row>
+    <row r="22" spans="1:13" ht="30">
+      <c r="A22" s="55"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="21" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="50">
+        <v>25</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="53">
+        <v>1</v>
+      </c>
+      <c r="H23" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I23" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="54"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I24" s="54"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="54"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I25" s="54"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="54"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="54"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="55"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I27" s="55"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+    </row>
+    <row r="28" spans="1:13" ht="28.5">
+      <c r="A28" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="18">
+        <v>10</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+    </row>
+    <row r="29" spans="1:13" ht="30">
+      <c r="A29" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="50"/>
+      <c r="C29" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="53">
+        <v>1</v>
+      </c>
+      <c r="H29" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+    </row>
+    <row r="30" spans="1:13" ht="30">
+      <c r="A30" s="59"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+    </row>
+    <row r="31" spans="1:13" ht="30">
+      <c r="A31" s="59"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" ht="30">
+      <c r="A32" s="59"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+    </row>
+    <row r="33" spans="1:13" ht="30">
+      <c r="A33" s="60"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="50"/>
+      <c r="C34" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="50">
+        <v>1.5</v>
+      </c>
+      <c r="H34" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I34" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I35" s="54"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="59"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I36" s="54"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="59"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="54"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="60"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I38" s="55"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="18">
+        <v>1</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+    </row>
+    <row r="40" spans="1:13" ht="30">
+      <c r="A40" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="56"/>
+      <c r="C40" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" s="50">
+        <v>0.7</v>
+      </c>
+      <c r="H40" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+    </row>
+    <row r="41" spans="1:13" ht="30">
+      <c r="A41" s="51"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+    </row>
+    <row r="42" spans="1:13" ht="30">
+      <c r="A42" s="51"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+    </row>
+    <row r="43" spans="1:13" ht="30">
+      <c r="A43" s="51"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="23"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" ht="30">
+      <c r="A44" s="52"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="53">
+        <v>1</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" s="50">
+        <v>0.8</v>
+      </c>
+      <c r="H45" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I45" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I46" s="54"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I47" s="54"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="23"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="54"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="55"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I49" s="55"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+    </row>
+    <row r="50" spans="1:13" ht="28.5">
+      <c r="A50" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="18">
+        <v>25</v>
+      </c>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+    </row>
+    <row r="51" spans="1:13" ht="30">
+      <c r="A51" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="56"/>
+      <c r="C51" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+    </row>
+    <row r="52" spans="1:13" ht="30">
+      <c r="A52" s="54"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I52" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+    </row>
+    <row r="53" spans="1:13" ht="30">
+      <c r="A53" s="54"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I53" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+    </row>
+    <row r="54" spans="1:13" ht="30">
+      <c r="A54" s="54"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" s="23" t="e">
+        <f>#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E54" s="54"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I54" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+    </row>
+    <row r="55" spans="1:13" ht="30">
+      <c r="A55" s="55"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I55" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="53">
+        <v>25</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G56" s="50">
+        <v>0.3</v>
+      </c>
+      <c r="H56" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I56" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="22"/>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="54"/>
+      <c r="B57" s="54"/>
+      <c r="C57" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I57" s="54"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I58" s="54"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="54"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D59" s="23" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I59" s="54"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="55"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="23" t="e">
+        <f>[1]Đạn!#REF!+[1]Đạn!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E60" s="55"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I60" s="55"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="K1:M2"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="G1:G5"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="G18:G22"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="I23:I27"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="G23:G27"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="E56:E60"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5507F-02BA-4790-AB88-8656D327FB49}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="71" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="75"/>
+      <c r="B2" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="75"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="76"/>
+      <c r="B3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+    </row>
+    <row r="4" spans="1:14" ht="25.5">
+      <c r="A4" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="L4" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="M4" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="N4" s="77"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80">
+        <f>C6+C10</f>
+        <v>8</v>
+      </c>
+      <c r="D5" s="80" t="e">
+        <f>(D6+D10)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="80" t="e">
+        <f t="shared" ref="E5:J5" si="0">E6+E10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J5" s="80" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K5" s="79"/>
+      <c r="L5" s="80" t="e">
+        <f>E5+J5</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M5" s="81">
+        <v>63</v>
+      </c>
+      <c r="N5" s="79"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80">
+        <f>C7+C8+C9</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="80" t="e">
+        <f>(D7+D8+D9)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="80" t="e">
+        <f t="shared" ref="E6:I6" si="1">E7+E8+E9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F6" s="80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I6" s="80" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J6" s="80" t="e">
+        <f>F6+G6+H6+I6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K6" s="79"/>
+      <c r="L6" s="80" t="e">
+        <f t="shared" ref="L6:L13" si="2">E6+J6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+    </row>
+    <row r="7" spans="1:14" ht="30">
+      <c r="A7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80">
+        <f>[2]Đạn!B10+[2]Đạn!E10+[2]Đạn!B11+[2]Đạn!E11</f>
+        <v>2.5</v>
+      </c>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80">
+        <f>B7+C7+D7</f>
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80">
+        <f t="shared" ref="J7:J13" si="3">F7+G7+H7+I7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="79"/>
+      <c r="L7" s="80">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="79"/>
+      <c r="C8" s="82">
+        <f>[2]Đạn!B16+[2]Đạn!E16+[2]Đạn!B22+[2]Đạn!E22</f>
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="82" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="82" t="e">
+        <f>B8+C8+D8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="80" t="e">
+        <f>(#REF!+#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J8" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K8" s="79"/>
+      <c r="L8" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+    </row>
+    <row r="9" spans="1:14" ht="30">
+      <c r="A9" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80">
+        <f>B9+C9+D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="79"/>
+      <c r="L9" s="80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="79"/>
+      <c r="C10" s="80">
+        <f>C11+C12+C13</f>
+        <v>3</v>
+      </c>
+      <c r="D10" s="80" t="e">
+        <f>(D11+D12+D13)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="80" t="e">
+        <f t="shared" ref="E10:I10" si="4">E11+E12+E13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F10" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I10" s="80" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="J10" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K10" s="79"/>
+      <c r="L10" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M10" s="81">
+        <v>63</v>
+      </c>
+      <c r="N10" s="79"/>
+    </row>
+    <row r="11" spans="1:14" ht="30">
+      <c r="A11" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80">
+        <f>[2]Đạn!H10+[2]Đạn!H11</f>
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="83"/>
+      <c r="E11" s="80">
+        <f>B11+C11+D11</f>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="79"/>
+      <c r="L11" s="80">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="84"/>
+      <c r="C12" s="85">
+        <f>[2]Đạn!H16+[2]Đạn!H22</f>
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="80" t="e">
+        <f t="shared" ref="E12:E13" si="5">B12+C12+D12</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="85" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J12" s="80" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="K12" s="84"/>
+      <c r="L12" s="80" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="M12" s="84">
+        <v>63</v>
+      </c>
+      <c r="N12" s="84"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="84" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="86"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="80">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="84"/>
+      <c r="L13" s="80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="9" width="8.88671875" customWidth="1"/>
+    <col min="5" max="9" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38" t="s">
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="38" t="s">
+      <c r="K1" s="66"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-    </row>
-    <row r="2" spans="1:17" ht="32.4" customHeight="1" thickBot="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40" t="s">
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="67"/>
+    </row>
+    <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="27" thickBot="1">
-      <c r="A3" s="41" t="s">
+    <row r="3" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-    </row>
-    <row r="4" spans="1:17" ht="27" thickBot="1">
-      <c r="A4" s="41" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-    </row>
-    <row r="5" spans="1:17" ht="27" thickBot="1">
-      <c r="A5" s="44">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="10">
         <v>9</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="16">
         <v>8</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="16">
         <v>1</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="47">
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17">
         <v>1</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46">
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16">
         <v>1</v>
       </c>
-      <c r="N5" s="46">
-        <v>0</v>
-      </c>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46">
+      <c r="N5" s="16">
+        <v>0</v>
+      </c>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="27" thickBot="1">
-      <c r="A6" s="44">
+    <row r="6" spans="1:17" ht="15.75" thickBot="1">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="10">
         <v>4</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="16">
         <v>9</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="16">
         <v>1</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47">
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17">
         <v>1</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16">
         <v>1</v>
       </c>
-      <c r="N6" s="46">
-        <v>0</v>
-      </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46">
+      <c r="N6" s="16">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="27" thickBot="1">
-      <c r="A7" s="44">
+    <row r="7" spans="1:17" ht="15.75" thickBot="1">
+      <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="10">
         <v>4</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="16">
         <v>9</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="16">
         <v>1</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17">
         <v>1</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16">
         <v>1</v>
       </c>
-      <c r="N7" s="46">
-        <v>0</v>
-      </c>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46">
+      <c r="N7" s="16">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="27" thickBot="1">
-      <c r="A8" s="44">
+    <row r="8" spans="1:17" ht="15.75" thickBot="1">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="10">
         <v>8</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="16">
         <v>9</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="16">
         <v>1</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="47">
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17">
         <v>1</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16">
         <v>1</v>
       </c>
-      <c r="N8" s="46">
-        <v>0</v>
-      </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46">
+      <c r="N8" s="16">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="27" thickBot="1">
-      <c r="A9" s="44">
+    <row r="9" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="10">
         <v>9</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="16">
         <v>7.5</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="16">
         <v>1</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17">
         <v>1</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16">
         <v>1</v>
       </c>
-      <c r="N9" s="46">
-        <v>0</v>
-      </c>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46">
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1">
-      <c r="A10" s="44">
+    <row r="10" spans="1:17" ht="15.75" thickBot="1">
+      <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="10">
         <v>72</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="16">
         <v>2</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="16">
         <v>1</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="16">
         <v>1</v>
       </c>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47">
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17">
         <v>2</v>
       </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46">
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16">
         <v>1</v>
       </c>
-      <c r="N10" s="46">
+      <c r="N10" s="16">
         <v>1</v>
       </c>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46">
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="27" thickBot="1">
-      <c r="A11" s="44">
+    <row r="11" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A11" s="14">
         <v>7</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="10">
         <v>8</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="16">
         <v>2</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="16">
         <v>1</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17">
         <v>1</v>
       </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46">
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16">
         <v>1</v>
       </c>
-      <c r="N11" s="46">
-        <v>0</v>
-      </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46">
+      <c r="N11" s="16">
+        <v>0</v>
+      </c>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="27" thickBot="1">
-      <c r="A12" s="44">
+    <row r="12" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A12" s="14">
         <v>8</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="10">
         <v>36</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="16">
         <v>2</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="16">
         <v>1</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17">
         <v>1</v>
       </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46">
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16">
         <v>1</v>
       </c>
-      <c r="N12" s="46">
-        <v>0</v>
-      </c>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46">
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="27" thickBot="1">
-      <c r="A13" s="44">
+    <row r="13" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A13" s="14">
         <v>9</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="10">
         <v>486</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="16">
         <v>2</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="16">
         <v>7</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="16">
         <v>3</v>
       </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47">
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17">
         <v>10</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46">
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16">
         <v>7</v>
       </c>
-      <c r="N13" s="46">
+      <c r="N13" s="16">
         <v>3</v>
       </c>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46">
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" thickBot="1">
-      <c r="A14" s="44">
+    <row r="14" spans="1:17" ht="26.25" thickBot="1">
+      <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="10">
         <v>42</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="16">
         <v>2</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="16">
         <v>1</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47">
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17">
         <v>1</v>
       </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46">
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16">
         <v>1</v>
       </c>
-      <c r="N14" s="46">
-        <v>0</v>
-      </c>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46">
+      <c r="N14" s="16">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16">
         <v>1</v>
       </c>
     </row>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -8,19 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA880EF-3531-40F3-996F-AE82FCABBEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2AE13E-7E8F-4102-9BD3-17DC81180153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="3495" windowWidth="21600" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3015" yWindow="3795" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
-    <sheet name="KeHoachBaoDamQuanY" sheetId="9" r:id="rId2"/>
-    <sheet name="BaoDamQuanY" sheetId="13" r:id="rId3"/>
-    <sheet name="KeHoach9.2" sheetId="12" r:id="rId4"/>
-    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId5"/>
+    <sheet name="KeHoach9.2" sheetId="12" r:id="rId2"/>
+    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -108,70 +106,10 @@
     <t>Nội dung</t>
   </si>
   <si>
-    <t>Quân số</t>
-  </si>
-  <si>
-    <t>Dự kiến tỷ lệ TBB</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>BB</t>
-  </si>
-  <si>
-    <t>%QS</t>
-  </si>
-  <si>
-    <t>Số người</t>
-  </si>
-  <si>
-    <t>TBHH</t>
-  </si>
-  <si>
     <t>Người</t>
   </si>
   <si>
     <t>Toàn trận</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Hướng chủ yếu</t>
-  </si>
-  <si>
-    <t>Hướng thứ yếu</t>
-  </si>
-  <si>
-    <t>Ngày cao nhất</t>
-  </si>
-  <si>
-    <t>Phòng ngự phía sau</t>
-  </si>
-  <si>
-    <t>CĐ vòng ngoài</t>
-  </si>
-  <si>
-    <t>Dự bị cơ động</t>
-  </si>
-  <si>
-    <t>LL còn lại</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Phân bổ chuyển thương</t>
-  </si>
-  <si>
-    <t>Cáng bộ</t>
-  </si>
-  <si>
-    <t>Tự đi</t>
-  </si>
-  <si>
-    <t>Tổng</t>
   </si>
   <si>
     <t>Loại TBKT</t>
@@ -305,7 +243,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,31 +262,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -401,7 +314,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,12 +329,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -429,12 +336,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,200 +609,148 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1244,42 +1093,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="39"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="32"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="33"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1683,1303 +1532,472 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC69830-15C2-40EF-A85C-0B734C645A25}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="51"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="52" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="45"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <f>ROUND(C5*D5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <f>ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <f>ROUND(H5*C5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <f>E5+I5</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <f>ROUNDUP(J5/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="9">
-        <f>J5-K5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <f>J5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24">
-      <c r="A6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="6">
-        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="6">
-        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="6">
-        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" ref="K6:K11" si="4">ROUNDUP(J6/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="9">
-        <f t="shared" ref="L6:L11" si="5">J6-K6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
-        <f t="shared" ref="M6:M11" si="6">J6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24">
-      <c r="A8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="24">
-      <c r="A9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24">
-      <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="6">
-        <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <f>ROUND(C12*D12/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1034396D-DE56-46FD-A40B-D9B156937D93}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="43" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="45"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <f>ROUND(C5*D5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <f>ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <f>ROUND(H5*C5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <f>E5+I5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="24">
-      <c r="A6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6">
-        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="24">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="24">
-      <c r="A8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
-        <v>3</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="24">
-      <c r="A9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="7">
-        <v>4</v>
-      </c>
-      <c r="G9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>4</v>
-      </c>
-      <c r="I9" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="24">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="7">
-        <v>5</v>
-      </c>
-      <c r="G10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>5</v>
-      </c>
-      <c r="I10" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="7">
-        <v>6</v>
-      </c>
-      <c r="G11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>6</v>
-      </c>
-      <c r="I11" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="24">
-      <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="6">
-        <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>8</v>
-      </c>
-      <c r="E12" s="6">
-        <f>ROUND(C12*D12/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5507F-02BA-4790-AB88-8656D327FB49}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="55" t="s">
-        <v>69</v>
+      <c r="B1" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="37" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="56"/>
-      <c r="B2" s="58" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="56"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="38"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="57"/>
-      <c r="B3" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="20" t="s">
+      <c r="F3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
     </row>
     <row r="4" spans="1:14" ht="25.5">
-      <c r="A4" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="21"/>
+      <c r="A4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24">
+      <c r="A5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18">
         <f>C6+C10</f>
         <v>8</v>
       </c>
-      <c r="D5" s="24" t="e">
+      <c r="D5" s="18" t="e">
         <f>(D6+D10)</f>
         <v>#REF!</v>
       </c>
-      <c r="E5" s="24" t="e">
+      <c r="E5" s="18" t="e">
         <f t="shared" ref="E5:J5" si="0">E6+E10</f>
         <v>#REF!</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="24" t="e">
+      <c r="G5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="H5" s="24" t="e">
+      <c r="H5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I5" s="24" t="e">
+      <c r="I5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="J5" s="24" t="e">
+      <c r="J5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="24" t="e">
+      <c r="K5" s="17"/>
+      <c r="L5" s="18" t="e">
         <f>E5+J5</f>
         <v>#REF!</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="19">
         <v>63</v>
       </c>
-      <c r="N5" s="23"/>
+      <c r="N5" s="17"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24">
+      <c r="A6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18">
         <f>C7+C8+C9</f>
         <v>5</v>
       </c>
-      <c r="D6" s="24" t="e">
+      <c r="D6" s="18" t="e">
         <f>(D7+D8+D9)</f>
         <v>#REF!</v>
       </c>
-      <c r="E6" s="24" t="e">
+      <c r="E6" s="18" t="e">
         <f t="shared" ref="E6:I6" si="1">E7+E8+E9</f>
         <v>#REF!</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="24" t="e">
+      <c r="G6" s="18" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="H6" s="24" t="e">
+      <c r="H6" s="18" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="I6" s="24" t="e">
+      <c r="I6" s="18" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="24" t="e">
+      <c r="J6" s="18" t="e">
         <f>F6+G6+H6+I6</f>
         <v>#REF!</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24" t="e">
+      <c r="K6" s="17"/>
+      <c r="L6" s="18" t="e">
         <f t="shared" ref="L6:L13" si="2">E6+J6</f>
         <v>#REF!</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14" ht="30">
-      <c r="A7" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24">
+      <c r="A7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18">
         <f>[1]Đạn!B10+[1]Đạn!E10+[1]Đạn!B11+[1]Đạn!E11</f>
         <v>2.5</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18">
         <f>B7+C7+D7</f>
         <v>2.5</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24">
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18">
         <f t="shared" ref="J7:J13" si="3">F7+G7+H7+I7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24">
+      <c r="K7" s="17"/>
+      <c r="L7" s="18">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="26">
+      <c r="A8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="20">
         <f>[1]Đạn!B16+[1]Đạn!E16+[1]Đạn!B22+[1]Đạn!E22</f>
         <v>2.5</v>
       </c>
-      <c r="D8" s="26" t="e">
+      <c r="D8" s="20" t="e">
         <f>(#REF!+#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E8" s="26" t="e">
+      <c r="E8" s="20" t="e">
         <f>B8+C8+D8</f>
         <v>#REF!</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24" t="e">
+      <c r="F8" s="18"/>
+      <c r="G8" s="18" t="e">
         <f>(#REF!+#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H8" s="24" t="e">
+      <c r="H8" s="18" t="e">
         <f>(#REF!+#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="I8" s="24" t="e">
+      <c r="I8" s="18" t="e">
         <f>(#REF!+#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J8" s="24" t="e">
+      <c r="J8" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24" t="e">
+      <c r="K8" s="17"/>
+      <c r="L8" s="18" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" ht="30">
-      <c r="A9" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24">
+      <c r="A9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18">
         <f>B9+C9+D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24">
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24">
+      <c r="K9" s="17"/>
+      <c r="L9" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24">
+      <c r="A10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18">
         <f>C11+C12+C13</f>
         <v>3</v>
       </c>
-      <c r="D10" s="24" t="e">
+      <c r="D10" s="18" t="e">
         <f>(D11+D12+D13)</f>
         <v>#REF!</v>
       </c>
-      <c r="E10" s="24" t="e">
+      <c r="E10" s="18" t="e">
         <f t="shared" ref="E10:I10" si="4">E11+E12+E13</f>
         <v>#REF!</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G10" s="24" t="e">
+      <c r="G10" s="18" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="H10" s="24" t="e">
+      <c r="H10" s="18" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="I10" s="24" t="e">
+      <c r="I10" s="18" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="J10" s="24" t="e">
+      <c r="J10" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24" t="e">
+      <c r="K10" s="17"/>
+      <c r="L10" s="18" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="19">
         <v>63</v>
       </c>
-      <c r="N10" s="23"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="30">
-      <c r="A11" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24">
+      <c r="A11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18">
         <f>[1]Đạn!H10+[1]Đạn!H11</f>
         <v>1.5</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="24">
+      <c r="D11" s="21"/>
+      <c r="E11" s="18">
         <f>B11+C11+D11</f>
         <v>1.5</v>
       </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24">
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24">
+      <c r="K11" s="17"/>
+      <c r="L11" s="18">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29">
+      <c r="A12" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23">
         <f>[1]Đạn!H16+[1]Đạn!H22</f>
         <v>1.5</v>
       </c>
-      <c r="D12" s="29" t="e">
+      <c r="D12" s="23" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="24" t="e">
+      <c r="E12" s="18" t="e">
         <f t="shared" ref="E12:E13" si="5">B12+C12+D12</f>
         <v>#REF!</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29" t="e">
+      <c r="F12" s="23"/>
+      <c r="G12" s="23" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" s="29" t="e">
+      <c r="H12" s="23" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="29" t="e">
+      <c r="I12" s="23" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J12" s="24" t="e">
+      <c r="J12" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K12" s="28"/>
-      <c r="L12" s="24" t="e">
+      <c r="K12" s="22"/>
+      <c r="L12" s="18" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="22">
         <v>63</v>
       </c>
-      <c r="N12" s="28"/>
+      <c r="N12" s="22"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="24">
+      <c r="A13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="24">
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="28"/>
-      <c r="L13" s="24">
+      <c r="K13" s="22"/>
+      <c r="L13" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2996,7 +2014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3005,500 +2023,500 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="64" t="s">
+      <c r="B1" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="66" t="s">
+      <c r="D1" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="63"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
     </row>
     <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A5" s="14">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="4">
         <v>9</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="10">
         <v>8</v>
       </c>
-      <c r="E5" s="16">
-        <v>1</v>
-      </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16">
-        <v>1</v>
-      </c>
-      <c r="N5" s="16">
-        <v>0</v>
-      </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10">
+        <v>1</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A6" s="14">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="10">
+      <c r="B6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4">
         <v>4</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="10">
         <v>9</v>
       </c>
-      <c r="E6" s="16">
-        <v>1</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17">
-        <v>1</v>
-      </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16">
-        <v>1</v>
-      </c>
-      <c r="N6" s="16">
-        <v>0</v>
-      </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16">
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="11">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10">
+        <v>1</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A7" s="14">
+      <c r="A7" s="8">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="10">
+      <c r="B7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="10">
         <v>9</v>
       </c>
-      <c r="E7" s="16">
-        <v>1</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16">
-        <v>1</v>
-      </c>
-      <c r="N7" s="16">
-        <v>0</v>
-      </c>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A8" s="14">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="B8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4">
         <v>8</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="10">
         <v>9</v>
       </c>
-      <c r="E8" s="16">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17">
-        <v>1</v>
-      </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16">
-        <v>1</v>
-      </c>
-      <c r="N8" s="16">
-        <v>0</v>
-      </c>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16">
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="11">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A9" s="14">
+      <c r="A9" s="8">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="4">
         <v>9</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="10">
         <v>7.5</v>
       </c>
-      <c r="E9" s="16">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17">
-        <v>1</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16">
-        <v>1</v>
-      </c>
-      <c r="N9" s="16">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16">
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="11">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A10" s="14">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="4">
         <v>72</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="10">
         <v>2</v>
       </c>
-      <c r="E10" s="16">
-        <v>1</v>
-      </c>
-      <c r="F10" s="16">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17">
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="11">
         <v>2</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16">
-        <v>1</v>
-      </c>
-      <c r="N10" s="16">
-        <v>1</v>
-      </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16">
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A11" s="14">
+      <c r="A11" s="8">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="10">
+      <c r="B11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="4">
         <v>8</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="10">
         <v>2</v>
       </c>
-      <c r="E11" s="16">
-        <v>1</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17">
-        <v>1</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16">
-        <v>1</v>
-      </c>
-      <c r="N11" s="16">
-        <v>0</v>
-      </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16">
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A12" s="14">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="10">
+      <c r="B12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="4">
         <v>36</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="16">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17">
-        <v>1</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16">
-        <v>1</v>
-      </c>
-      <c r="N12" s="16">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16">
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="11">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A13" s="14">
+      <c r="A13" s="8">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="10">
+      <c r="B13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4">
         <v>486</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="10">
         <v>7</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="10">
         <v>3</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="11">
         <v>10</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16">
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10">
         <v>7</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="10">
         <v>3</v>
       </c>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16">
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="26.25" thickBot="1">
-      <c r="A14" s="14">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="4">
         <v>42</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14" s="16">
-        <v>1</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17">
-        <v>1</v>
-      </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16">
-        <v>1</v>
-      </c>
-      <c r="N14" s="16">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16">
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10">
         <v>1</v>
       </c>
     </row>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2AE13E-7E8F-4102-9BD3-17DC81180153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="3795" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -5,21 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2AE13E-7E8F-4102-9BD3-17DC81180153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0A4405-30BD-43DC-9953-F9AEF028C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
-    <sheet name="KeHoach9.2" sheetId="12" r:id="rId2"/>
-    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId3"/>
+    <sheet name="KeHoachSuaChua" sheetId="10" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -103,15 +99,6 @@
     <t>Pháo PK 12.7</t>
   </si>
   <si>
-    <t>Nội dung</t>
-  </si>
-  <si>
-    <t>Người</t>
-  </si>
-  <si>
-    <t>Toàn trận</t>
-  </si>
-  <si>
     <t>Loại TBKT</t>
   </si>
   <si>
@@ -167,83 +154,13 @@
   </si>
   <si>
     <t>Súng tiểu liên</t>
-  </si>
-  <si>
-    <t>QN</t>
-  </si>
-  <si>
-    <t>QY</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>VTKT</t>
-  </si>
-  <si>
-    <t>Đạn</t>
-  </si>
-  <si>
-    <t>Khối lượng vận chuyển</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>Vũ khí trang bị kỹ thuật</t>
-  </si>
-  <si>
-    <t>Vật chất hậu cần</t>
-  </si>
-  <si>
-    <t>Vật chất khác</t>
-  </si>
-  <si>
-    <t>Cộng</t>
-  </si>
-  <si>
-    <t>VKTB</t>
-  </si>
-  <si>
-    <t>XD</t>
-  </si>
-  <si>
-    <t>Đơn vị tính</t>
-  </si>
-  <si>
-    <t>tấn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tấn </t>
-  </si>
-  <si>
-    <t>người</t>
-  </si>
-  <si>
-    <t>GĐCB</t>
-  </si>
-  <si>
-    <t>Trên chuyển</t>
-  </si>
-  <si>
-    <t>Cấp mình</t>
-  </si>
-  <si>
-    <t>Dưới chuyển</t>
-  </si>
-  <si>
-    <t>GĐCĐ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-  </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,26 +210,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -346,7 +243,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -442,43 +339,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -609,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -620,83 +480,46 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -717,40 +540,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,64 +573,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="QUÂN SỐ"/>
-      <sheetName val="1. QS, TBKT"/>
-      <sheetName val="Đạn"/>
-      <sheetName val="VCHC, VTKT"/>
-      <sheetName val="Giao diện"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="10">
-          <cell r="B10">
-            <v>0</v>
-          </cell>
-          <cell r="E10">
-            <v>0</v>
-          </cell>
-          <cell r="H10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>1.25</v>
-          </cell>
-          <cell r="E11">
-            <v>1.25</v>
-          </cell>
-          <cell r="H11">
-            <v>1.5</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>1.25</v>
-          </cell>
-          <cell r="E16">
-            <v>1.25</v>
-          </cell>
-          <cell r="H16">
-            <v>1.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1093,42 +840,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="26"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="36"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="27"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1532,489 +1279,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5507F-02BA-4790-AB88-8656D327FB49}">
-  <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="38"/>
-      <c r="B2" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="38"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="39"/>
-      <c r="B3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-    </row>
-    <row r="4" spans="1:14" ht="25.5">
-      <c r="A4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18">
-        <f>C6+C10</f>
-        <v>8</v>
-      </c>
-      <c r="D5" s="18" t="e">
-        <f>(D6+D10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="18" t="e">
-        <f t="shared" ref="E5:J5" si="0">E6+E10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F5" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H5" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I5" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J5" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="18" t="e">
-        <f>E5+J5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M5" s="19">
-        <v>63</v>
-      </c>
-      <c r="N5" s="17"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18">
-        <f>C7+C8+C9</f>
-        <v>5</v>
-      </c>
-      <c r="D6" s="18" t="e">
-        <f>(D7+D8+D9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="18" t="e">
-        <f t="shared" ref="E6:I6" si="1">E7+E8+E9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H6" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" s="18" t="e">
-        <f>F6+G6+H6+I6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18" t="e">
-        <f t="shared" ref="L6:L13" si="2">E6+J6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-    </row>
-    <row r="7" spans="1:14" ht="30">
-      <c r="A7" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18">
-        <f>[1]Đạn!B10+[1]Đạn!E10+[1]Đạn!B11+[1]Đạn!E11</f>
-        <v>2.5</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18">
-        <f>B7+C7+D7</f>
-        <v>2.5</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18">
-        <f t="shared" ref="J7:J13" si="3">F7+G7+H7+I7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="18">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="20">
-        <f>[1]Đạn!B16+[1]Đạn!E16+[1]Đạn!B22+[1]Đạn!E22</f>
-        <v>2.5</v>
-      </c>
-      <c r="D8" s="20" t="e">
-        <f>(#REF!+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E8" s="20" t="e">
-        <f>B8+C8+D8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18" t="e">
-        <f>(#REF!+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H8" s="18" t="e">
-        <f>(#REF!+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="18" t="e">
-        <f>(#REF!+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" ht="30">
-      <c r="A9" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18">
-        <f>B9+C9+D9</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18">
-        <f>C11+C12+C13</f>
-        <v>3</v>
-      </c>
-      <c r="D10" s="18" t="e">
-        <f>(D11+D12+D13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E10" s="18" t="e">
-        <f t="shared" ref="E10:I10" si="4">E11+E12+E13</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F10" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H10" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I10" s="18" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J10" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="M10" s="19">
-        <v>63</v>
-      </c>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" ht="30">
-      <c r="A11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18">
-        <f>[1]Đạn!H10+[1]Đạn!H11</f>
-        <v>1.5</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="18">
-        <f>B11+C11+D11</f>
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18">
-        <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23">
-        <f>[1]Đạn!H16+[1]Đạn!H22</f>
-        <v>1.5</v>
-      </c>
-      <c r="D12" s="23" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E12" s="18" t="e">
-        <f t="shared" ref="E12:E13" si="5">B12+C12+D12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H12" s="23" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I12" s="23" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J12" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="18" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="M12" s="22">
-        <v>63</v>
-      </c>
-      <c r="N12" s="22"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2023,51 +1287,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="25"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="46" t="s">
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="26"/>
+    </row>
+    <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="45"/>
-    </row>
-    <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>12</v>
@@ -2102,10 +1366,10 @@
     </row>
     <row r="3" spans="1:17" ht="26.25" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2125,10 +1389,10 @@
     </row>
     <row r="4" spans="1:17" ht="26.25" thickBot="1">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2151,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4">
         <v>9</v>
@@ -2188,7 +1452,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4">
         <v>4</v>
@@ -2225,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
@@ -2262,7 +1526,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4">
         <v>8</v>
@@ -2299,7 +1563,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4">
         <v>9</v>
@@ -2336,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4">
         <v>72</v>
@@ -2375,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4">
         <v>8</v>
@@ -2412,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4">
         <v>36</v>
@@ -2449,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C13" s="4">
         <v>486</v>

--- a/Resources/Sheet/Book2.xlsx
+++ b/Resources/Sheet/Book2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0A4405-30BD-43DC-9953-F9AEF028C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0078C594-639E-403B-85C8-9CF75E8B8094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuaChua" sheetId="7" r:id="rId1"/>
@@ -560,7 +560,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -834,9 +834,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A12AC3B-8D90-4B0D-96EA-52FB68143200}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -906,15 +906,15 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <f>ROUNDUP(I4*0.5,0)</f>
+        <f>ROUND(C4*D4/2,0)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <f>ROUND(I4*0.25,0)</f>
+        <f>ROUND(C4*D4/4,0)</f>
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <f>ROUND(I4*0.15,0)</f>
+        <f>ROUND(C4*D4*15/100,0)</f>
         <v>0</v>
       </c>
       <c r="H4" s="2">
@@ -940,23 +940,23 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <f t="shared" ref="E5:E8" si="0">ROUNDUP(I5*0.5,0)</f>
+        <f t="shared" ref="E5:E14" si="0">ROUND(C5*D5/2,0)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" ref="F5:F8" si="1">ROUND(I5*0.25,0)</f>
+        <f t="shared" ref="F5:F14" si="1">ROUND(C5*D5/4,0)</f>
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:G8" si="2">ROUND(I5*0.15,0)</f>
+        <f>ROUND(C5*D5*15/100,0)</f>
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" ref="H5:H8" si="3">I5-E5-F5-G5</f>
+        <f t="shared" ref="H5:H14" si="2">I5-E5-F5-G5</f>
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" ref="I5:I8" si="4">ROUND(C5*D5/100,0)</f>
+        <f t="shared" ref="I5:I8" si="3">ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -982,15 +982,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
+        <f t="shared" ref="G6:G14" si="4">ROUND(C6*D6*15/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -1016,15 +1016,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -1050,15 +1050,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <f t="shared" ref="E9:E11" si="5">ROUNDUP(I9*0.5,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" ref="F9:F11" si="6">ROUND(I9*0.25,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" ref="G9:G11" si="7">ROUND(I9*0.15,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" ref="H9:H11" si="8">I9-E9-F9-G9</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" ref="I9:I11" si="9">ROUND(C9*D9/100,0)</f>
+        <f t="shared" ref="I9:I11" si="5">ROUND(C9*D9/100,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1110,23 +1110,23 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -1144,23 +1144,23 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -1178,23 +1178,23 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" ref="E12:E14" si="10">ROUNDUP(I12*0.5,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" ref="F12:F14" si="11">ROUND(I12*0.25,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" ref="G12:G14" si="12">ROUND(I12*0.15,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" ref="H12:H14" si="13">I12-E12-F12-G12</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" ref="I12:I14" si="14">ROUND(C12*D12/100,0)</f>
+        <f t="shared" ref="I12:I14" si="6">ROUND(C12*D12/100,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -1246,23 +1246,23 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -1281,9 +1281,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B17497-2FA8-4780-A781-D58241AE9548}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="9" width="8.85546875" customWidth="1"/>
+    <col min="5" max="9" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33.6" customHeight="1" thickBot="1">
@@ -1319,7 +1319,7 @@
       <c r="P1" s="25"/>
       <c r="Q1" s="26"/>
     </row>
-    <row r="2" spans="1:17" ht="32.450000000000003" customHeight="1" thickBot="1">
+    <row r="2" spans="1:17" ht="32.4" customHeight="1" thickBot="1">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -1364,7 +1364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="26.25" thickBot="1">
+    <row r="3" spans="1:17" ht="27" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>27</v>
       </c>
@@ -1387,7 +1387,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" ht="26.25" thickBot="1">
+    <row r="4" spans="1:17" ht="27" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
@@ -1410,7 +1410,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17" ht="26.25" thickBot="1">
+    <row r="5" spans="1:17" ht="27" thickBot="1">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1">
+    <row r="6" spans="1:17" ht="27" thickBot="1">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1">
+    <row r="7" spans="1:17" ht="27" thickBot="1">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1">
+    <row r="8" spans="1:17" ht="27" thickBot="1">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="26.25" thickBot="1">
+    <row r="9" spans="1:17" ht="27" thickBot="1">
       <c r="A9" s="8">
         <v>5</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" thickBot="1">
+    <row r="10" spans="1:17" ht="15" thickBot="1">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="26.25" thickBot="1">
+    <row r="11" spans="1:17" ht="27" thickBot="1">
       <c r="A11" s="8">
         <v>7</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="26.25" thickBot="1">
+    <row r="12" spans="1:17" ht="27" thickBot="1">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="26.25" thickBot="1">
+    <row r="13" spans="1:17" ht="27" thickBot="1">
       <c r="A13" s="8">
         <v>9</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="26.25" thickBot="1">
+    <row r="14" spans="1:17" ht="15" thickBot="1">
       <c r="A14" s="8">
         <v>10</v>
       </c>
